--- a/Dados/Brutos/valores_nominais/pib_mesos.xlsx
+++ b/Dados/Brutos/valores_nominais/pib_mesos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sistemafiesc-my.sharepoint.com/personal/arthur-calza_ielsc_org_br/Documents/Área de Trabalho/VS Code/proj_munic_sc/Dados/Brutos/valores_nominais/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{A9966A9F-58DA-4247-896B-72836C457173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E99FDBE-688E-4F61-B82B-9995B9F8B458}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{A9966A9F-58DA-4247-896B-72836C457173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CDB55265-6237-4421-8A85-D567B8FC0283}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="1536" yWindow="1104" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="reais" sheetId="3" r:id="rId1"/>
@@ -133,6 +133,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -425,12 +429,11 @@
   <dimension ref="A1:K23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="12" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9.109375" customWidth="1"/>
     <col min="18" max="19" width="12" bestFit="1" customWidth="1"/>
